--- a/docs/olap/Senior Care Management - ETL Mapping.xlsx
+++ b/docs/olap/Senior Care Management - ETL Mapping.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimDate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimSenior" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimProfessional" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimService" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimOrganization" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FactVisit" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DimDate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DimSenior" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DimProfessional" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DimService" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DimOrganization" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FactVisit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1 when both timestamps exist and visit is not Missed; otherwise 0.</t>
+          <t>1 when Status is not Cancelled, both timestamps exist and visit is not Missed; otherwise 0.</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -2256,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="28" customWidth="1" style="6" min="1" max="1"/>
@@ -2355,256 +2355,24 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" s="6">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Time-of-day gap</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>OLAP Query 3 requires Morning/Afternoon/Evening, but no TimeOfDay field or DimTime is shown in the OLAP ERD. FactVisit.TimeOfDay is marked PROPOSED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="6">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Unresolved terminology and schema issues</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="28.05" customHeight="1" s="6">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Issue Type</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Field / Naming</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Resolution or confirmation needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34.05" customHeight="1" s="6">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Visit vs SeniorServiceAppointment</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Confirmed assignment standardization; verify physical source table name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34.05" customHeight="1" s="6">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Caregiver vs MedicalProfessional</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Caregiver is the assignment term; OLTP ERD uses MedicalProfessional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34.05" customHeight="1" s="6">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Terminology</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Agency vs Organization</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Agency is the assignment term; OLTP/OLAP ERDs use Organization in places.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34.05" customHeight="1" s="6">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Visit fields</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>ScheduledStartTime vs ScheduledStart</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Naming equivalent; use ScheduledStartTime in OLTP mapping and ScheduledStart in query documentation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34.05" customHeight="1" s="6">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Visit fields</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>CheckInDateTime vs ActualCheckIn</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Naming equivalent; use CheckInDateTime in the standardized mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34.05" customHeight="1" s="6">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Visit fields</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>CheckOutDateTime vs ActualCheckOut</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Naming equivalent; use CheckOutDateTime in the standardized mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34.05" customHeight="1" s="6">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Visit fields</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>VisitStatus vs Status</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Naming equivalent; use VisitStatus in the standardized mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34.05" customHeight="1" s="6">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>AgeGroup storage</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Static DimSenior AgeGroup cannot preserve visit-date history; approve a FactVisit-derived band or historical dimension strategy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34.05" customHeight="1" s="6">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>TimeOfDay</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Required by Query 3 but proposed in FactVisit; Morning/Afternoon/Evening boundaries require group approval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34.05" customHeight="1" s="6">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>ServiceCategory</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>No authoritative OLTP category field; approved ServiceID-to-category mapping is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34.05" customHeight="1" s="6">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Caregiver-to-Agency and professional roles</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Confirm foreign-key/cardinality details and multi-role handling before production ETL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34.05" customHeight="1" s="6">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Source fields</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>DimSenior.City</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Confirm the source field and address parsing rule; the ERD does not show a dedicated OLTP City field.</t>
-        </is>
-      </c>
-    </row>
+    <row r="9" ht="42" customHeight="1" s="6"/>
+    <row r="10" ht="24" customHeight="1" s="6"/>
+    <row r="11" ht="28.05" customHeight="1" s="6"/>
+    <row r="12" ht="34.05" customHeight="1" s="6"/>
+    <row r="13" ht="34.05" customHeight="1" s="6"/>
+    <row r="14" ht="34.05" customHeight="1" s="6"/>
+    <row r="15" ht="34.05" customHeight="1" s="6"/>
+    <row r="16" ht="34.05" customHeight="1" s="6"/>
+    <row r="17" ht="34.05" customHeight="1" s="6"/>
+    <row r="18" ht="34.05" customHeight="1" s="6"/>
+    <row r="19" ht="34.05" customHeight="1" s="6"/>
+    <row r="20" ht="34.05" customHeight="1" s="6"/>
+    <row r="21" ht="34.05" customHeight="1" s="6"/>
+    <row r="22" ht="34.05" customHeight="1" s="6"/>
+    <row r="23" ht="34.05" customHeight="1" s="6"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
